--- a/docs/REPAIR01_20260823/11 · المراجعة الثانية.xlsx
+++ b/docs/REPAIR01_20260823/11 · المراجعة الثانية.xlsx
@@ -1052,7 +1052,7 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>391 مقابل 391</t>
+          <t>395 مقابل 395</t>
         </is>
       </c>
       <c r="E7" s="11" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>2059 حقلًا · يتيم 0</t>
+          <t>2103 حقلًا · يتيم 0</t>
         </is>
       </c>
       <c r="E18" s="11" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="D19" s="11" t="inlineStr">
         <is>
-          <t>req 119 · inv 119 · tobe 119</t>
+          <t>req 120 · inv 120 · tobe 120</t>
         </is>
       </c>
       <c r="E19" s="11" t="inlineStr">
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>أسطح 119 · حقول 2059</t>
+          <t>أسطح 120 · حقول 2103</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="D33" s="11" t="inlineStr">
         <is>
-          <t>1440 حقلًا · يتيم 0</t>
+          <t>1496 حقلًا · يتيم 0</t>
         </is>
       </c>
       <c r="E33" s="11" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="D34" s="11" t="inlineStr">
         <is>
-          <t>req 96 · inv 96 · tobe 96</t>
+          <t>req 99 · inv 99 · tobe 99</t>
         </is>
       </c>
       <c r="E34" s="11" t="inlineStr">
@@ -1976,7 +1976,7 @@
       </c>
       <c r="D36" s="11" t="inlineStr">
         <is>
-          <t>أسطح 96 · حقول 1440</t>
+          <t>أسطح 99 · حقول 1496</t>
         </is>
       </c>
       <c r="E36" s="11" t="inlineStr">
@@ -2200,7 +2200,7 @@
       </c>
       <c r="D43" s="11" t="inlineStr">
         <is>
-          <t>429 / 429</t>
+          <t>433 / 433</t>
         </is>
       </c>
       <c r="E43" s="11" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D46" s="11" t="inlineStr">
         <is>
-          <t>429 مقابل 429</t>
+          <t>433 مقابل 433</t>
         </is>
       </c>
       <c r="E46" s="11" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="D47" s="11" t="inlineStr">
         <is>
-          <t>7491 حقلًا · يتيم 0</t>
+          <t>7591 حقلًا · يتيم 0</t>
         </is>
       </c>
       <c r="E47" s="11" t="inlineStr">
@@ -3043,7 +3043,7 @@
       </c>
       <c r="E18" s="11" t="inlineStr">
         <is>
-          <t>اللوحة — خارج الدورة (Overview) ← دورة البلاغ ← السجلات التابعة</t>
+          <t>اللوحة — خارج الدورة (Overview) ← السجلات التابعة ← دورة البلاغ</t>
         </is>
       </c>
       <c r="F18" s="11" t="inlineStr">
@@ -51289,7 +51289,7 @@
         <v>50</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>6</v>
@@ -51529,7 +51529,7 @@
         <v>31</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D11" s="13" t="n">
         <v>4</v>
@@ -51811,7 +51811,7 @@
         <v>22</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D18" s="11" t="n">
         <v>3</v>
